--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:20</t>
+    <t xml:space="preserve">2026-10-05 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -619,7 +619,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>884106.12</v>
+        <v>884106.13</v>
       </c>
     </row>
     <row r="9">
